--- a/panchang-data/Jammu2026.xlsx
+++ b/panchang-data/Jammu2026.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5406">
   <si>
     <t>दिनाङ्क</t>
   </si>
@@ -16243,6 +16243,9 @@
   </si>
   <si>
     <t>121°05'00.36</t>
+  </si>
+  <si>
+    <t>ज्येष्ठ अधिक</t>
   </si>
 </sst>
 </file>
@@ -16732,7 +16735,7 @@
         <v>46023</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>29</v>
@@ -16818,7 +16821,7 @@
         <v>46024</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>51</v>
@@ -16904,7 +16907,7 @@
         <v>46025</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>70</v>
@@ -16990,7 +16993,7 @@
         <v>46026</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>89</v>
+        <v>570</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>90</v>
@@ -17076,7 +17079,7 @@
         <v>46027</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>570</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>108</v>
@@ -17162,7 +17165,7 @@
         <v>46028</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>89</v>
+        <v>570</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>126</v>
@@ -17248,7 +17251,7 @@
         <v>46029</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>89</v>
+        <v>570</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>144</v>
@@ -17334,7 +17337,7 @@
         <v>46030</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>89</v>
+        <v>570</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>29</v>
@@ -17420,7 +17423,7 @@
         <v>46031</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>89</v>
+        <v>570</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>51</v>
@@ -17506,7 +17509,7 @@
         <v>46032</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>89</v>
+        <v>570</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>70</v>
@@ -17592,7 +17595,7 @@
         <v>46033</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>89</v>
+        <v>570</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>90</v>
@@ -17678,7 +17681,7 @@
         <v>46034</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>89</v>
+        <v>570</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>108</v>
@@ -17764,7 +17767,7 @@
         <v>46035</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>89</v>
+        <v>570</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>126</v>
@@ -17850,7 +17853,7 @@
         <v>46036</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>89</v>
+        <v>570</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>144</v>
@@ -17936,7 +17939,7 @@
         <v>46037</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>89</v>
+        <v>570</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>29</v>
@@ -18022,7 +18025,7 @@
         <v>46038</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>89</v>
+        <v>570</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>51</v>
@@ -18108,7 +18111,7 @@
         <v>46039</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>89</v>
+        <v>570</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>70</v>
@@ -18194,7 +18197,7 @@
         <v>46040</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>89</v>
+        <v>570</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>90</v>
@@ -18280,7 +18283,7 @@
         <v>46041</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>89</v>
+        <v>570</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>108</v>
@@ -18366,7 +18369,7 @@
         <v>46042</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>89</v>
+        <v>570</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>126</v>
@@ -18452,7 +18455,7 @@
         <v>46043</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>89</v>
+        <v>570</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>144</v>
@@ -18538,7 +18541,7 @@
         <v>46044</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>89</v>
+        <v>570</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>29</v>
@@ -18624,7 +18627,7 @@
         <v>46045</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>89</v>
+        <v>570</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>51</v>
@@ -18710,7 +18713,7 @@
         <v>46046</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>89</v>
+        <v>570</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>70</v>
@@ -18796,7 +18799,7 @@
         <v>46047</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>89</v>
+        <v>570</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>90</v>
@@ -18882,7 +18885,7 @@
         <v>46048</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>89</v>
+        <v>570</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>108</v>
@@ -18968,7 +18971,7 @@
         <v>46049</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>89</v>
+        <v>570</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>126</v>
@@ -19054,7 +19057,7 @@
         <v>46050</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>89</v>
+        <v>570</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>144</v>
@@ -19140,7 +19143,7 @@
         <v>46051</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>89</v>
+        <v>570</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>29</v>
@@ -19226,7 +19229,7 @@
         <v>46052</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>89</v>
+        <v>570</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>51</v>
@@ -19312,7 +19315,7 @@
         <v>46053</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>89</v>
+        <v>570</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>70</v>
@@ -19398,7 +19401,7 @@
         <v>46054</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>89</v>
+        <v>570</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>90</v>
@@ -19484,7 +19487,7 @@
         <v>46055</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>570</v>
+        <v>1012</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>108</v>
@@ -19570,7 +19573,7 @@
         <v>46056</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>570</v>
+        <v>1012</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>126</v>
@@ -19656,7 +19659,7 @@
         <v>46057</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>570</v>
+        <v>1012</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>144</v>
@@ -19742,7 +19745,7 @@
         <v>46058</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>570</v>
+        <v>1012</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>29</v>
@@ -19828,7 +19831,7 @@
         <v>46059</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>570</v>
+        <v>1012</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>51</v>
@@ -19914,7 +19917,7 @@
         <v>46060</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>570</v>
+        <v>1012</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>70</v>
@@ -20000,7 +20003,7 @@
         <v>46061</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>570</v>
+        <v>1012</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>90</v>
@@ -20086,7 +20089,7 @@
         <v>46062</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>570</v>
+        <v>1012</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>108</v>
@@ -20172,7 +20175,7 @@
         <v>46063</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>570</v>
+        <v>1012</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>126</v>
@@ -20258,7 +20261,7 @@
         <v>46064</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>570</v>
+        <v>1012</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>144</v>
@@ -20344,7 +20347,7 @@
         <v>46065</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>570</v>
+        <v>1012</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>29</v>
@@ -20430,7 +20433,7 @@
         <v>46066</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>570</v>
+        <v>1012</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>51</v>
@@ -20516,7 +20519,7 @@
         <v>46067</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>570</v>
+        <v>1012</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>70</v>
@@ -20602,7 +20605,7 @@
         <v>46068</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>570</v>
+        <v>1012</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>90</v>
@@ -20688,7 +20691,7 @@
         <v>46069</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>570</v>
+        <v>1012</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>108</v>
@@ -20774,7 +20777,7 @@
         <v>46070</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>570</v>
+        <v>1012</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>126</v>
@@ -20860,7 +20863,7 @@
         <v>46071</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>570</v>
+        <v>1012</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>144</v>
@@ -20946,7 +20949,7 @@
         <v>46072</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>570</v>
+        <v>1012</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>29</v>
@@ -21032,7 +21035,7 @@
         <v>46073</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>570</v>
+        <v>1012</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>51</v>
@@ -21118,7 +21121,7 @@
         <v>46074</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>570</v>
+        <v>1012</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>70</v>
@@ -21204,7 +21207,7 @@
         <v>46075</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>570</v>
+        <v>1012</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>90</v>
@@ -21290,7 +21293,7 @@
         <v>46076</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>570</v>
+        <v>1012</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>108</v>
@@ -21376,7 +21379,7 @@
         <v>46077</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>570</v>
+        <v>1012</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>126</v>
@@ -21462,7 +21465,7 @@
         <v>46078</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>570</v>
+        <v>1012</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>144</v>
@@ -21548,7 +21551,7 @@
         <v>46079</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>570</v>
+        <v>1012</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>29</v>
@@ -21634,7 +21637,7 @@
         <v>46080</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>570</v>
+        <v>1012</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>51</v>
@@ -21720,7 +21723,7 @@
         <v>46081</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>570</v>
+        <v>1012</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>70</v>
@@ -21806,7 +21809,7 @@
         <v>46082</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>570</v>
+        <v>1012</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>90</v>
@@ -21892,7 +21895,7 @@
         <v>46083</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>570</v>
+        <v>1012</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>108</v>
@@ -21978,7 +21981,7 @@
         <v>46084</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>570</v>
+        <v>1012</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>126</v>
@@ -22064,7 +22067,7 @@
         <v>46085</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1012</v>
+        <v>1453</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>144</v>
@@ -22150,7 +22153,7 @@
         <v>46086</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>1012</v>
+        <v>1453</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>29</v>
@@ -22236,7 +22239,7 @@
         <v>46087</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1012</v>
+        <v>1453</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>51</v>
@@ -22322,7 +22325,7 @@
         <v>46088</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>1012</v>
+        <v>1453</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>70</v>
@@ -22408,7 +22411,7 @@
         <v>46089</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>1012</v>
+        <v>1453</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>90</v>
@@ -22494,7 +22497,7 @@
         <v>46090</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1012</v>
+        <v>1453</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>108</v>
@@ -22580,7 +22583,7 @@
         <v>46091</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>1012</v>
+        <v>1453</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>126</v>
@@ -22666,7 +22669,7 @@
         <v>46092</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>1012</v>
+        <v>1453</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>144</v>
@@ -22752,7 +22755,7 @@
         <v>46093</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>1012</v>
+        <v>1453</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>29</v>
@@ -22838,7 +22841,7 @@
         <v>46094</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>1012</v>
+        <v>1453</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>51</v>
@@ -22924,7 +22927,7 @@
         <v>46095</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>1012</v>
+        <v>1453</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>70</v>
@@ -23010,7 +23013,7 @@
         <v>46096</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>1012</v>
+        <v>1453</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>90</v>
@@ -23096,7 +23099,7 @@
         <v>46097</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>1012</v>
+        <v>1453</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>108</v>
@@ -23182,7 +23185,7 @@
         <v>46098</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>1012</v>
+        <v>1453</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>126</v>
@@ -23268,7 +23271,7 @@
         <v>46099</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>1012</v>
+        <v>1453</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>144</v>
@@ -23354,7 +23357,7 @@
         <v>46100</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>1012</v>
+        <v>1453</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>29</v>
@@ -23440,7 +23443,7 @@
         <v>46101</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>1012</v>
+        <v>1453</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>51</v>
@@ -23526,7 +23529,7 @@
         <v>46102</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>1012</v>
+        <v>1453</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>70</v>
@@ -23612,7 +23615,7 @@
         <v>46103</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>1012</v>
+        <v>1453</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>90</v>
@@ -23698,7 +23701,7 @@
         <v>46104</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>1012</v>
+        <v>1453</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>108</v>
@@ -23784,7 +23787,7 @@
         <v>46105</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>1012</v>
+        <v>1453</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>126</v>
@@ -23870,7 +23873,7 @@
         <v>46106</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>1012</v>
+        <v>1453</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>144</v>
@@ -23956,7 +23959,7 @@
         <v>46107</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>1012</v>
+        <v>1453</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>29</v>
@@ -24042,7 +24045,7 @@
         <v>46108</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>1012</v>
+        <v>1453</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>51</v>
@@ -24128,7 +24131,7 @@
         <v>46109</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>1012</v>
+        <v>1453</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>70</v>
@@ -24214,7 +24217,7 @@
         <v>46110</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>1012</v>
+        <v>1453</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>90</v>
@@ -24300,7 +24303,7 @@
         <v>46111</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>1012</v>
+        <v>1453</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>108</v>
@@ -24386,7 +24389,7 @@
         <v>46112</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>1012</v>
+        <v>1453</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>126</v>
@@ -24472,7 +24475,7 @@
         <v>46113</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>1012</v>
+        <v>1453</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>144</v>
@@ -24558,7 +24561,7 @@
         <v>46114</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>1012</v>
+        <v>1453</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>29</v>
@@ -24644,7 +24647,7 @@
         <v>46115</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>1453</v>
+        <v>1876</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>51</v>
@@ -24730,7 +24733,7 @@
         <v>46116</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>1453</v>
+        <v>1876</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>70</v>
@@ -24816,7 +24819,7 @@
         <v>46117</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>1453</v>
+        <v>1876</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>90</v>
@@ -24902,7 +24905,7 @@
         <v>46118</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>1453</v>
+        <v>1876</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>108</v>
@@ -24988,7 +24991,7 @@
         <v>46119</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>1453</v>
+        <v>1876</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>126</v>
@@ -25074,7 +25077,7 @@
         <v>46120</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>1453</v>
+        <v>1876</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>144</v>
@@ -25160,7 +25163,7 @@
         <v>46121</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>1453</v>
+        <v>1876</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>29</v>
@@ -25246,7 +25249,7 @@
         <v>46122</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1453</v>
+        <v>1876</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>51</v>
@@ -25332,7 +25335,7 @@
         <v>46123</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>1453</v>
+        <v>1876</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>70</v>
@@ -25418,7 +25421,7 @@
         <v>46124</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>1453</v>
+        <v>1876</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>90</v>
@@ -25504,7 +25507,7 @@
         <v>46125</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>1453</v>
+        <v>1876</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>108</v>
@@ -25590,7 +25593,7 @@
         <v>46126</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>1453</v>
+        <v>1876</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>126</v>
@@ -25676,7 +25679,7 @@
         <v>46127</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>1453</v>
+        <v>1876</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>144</v>
@@ -25762,7 +25765,7 @@
         <v>46128</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>1453</v>
+        <v>1876</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>29</v>
@@ -25848,7 +25851,7 @@
         <v>46129</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>1453</v>
+        <v>1876</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>51</v>
@@ -25934,7 +25937,7 @@
         <v>46130</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>1453</v>
+        <v>1876</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>70</v>
@@ -26020,7 +26023,7 @@
         <v>46131</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>1453</v>
+        <v>1876</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>90</v>
@@ -26106,7 +26109,7 @@
         <v>46132</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>1453</v>
+        <v>1876</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>108</v>
@@ -26192,7 +26195,7 @@
         <v>46133</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>1453</v>
+        <v>1876</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>126</v>
@@ -26278,7 +26281,7 @@
         <v>46134</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1453</v>
+        <v>1876</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>144</v>
@@ -26364,7 +26367,7 @@
         <v>46135</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>1453</v>
+        <v>1876</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>29</v>
@@ -26450,7 +26453,7 @@
         <v>46136</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>1453</v>
+        <v>1876</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>51</v>
@@ -26536,7 +26539,7 @@
         <v>46137</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>1453</v>
+        <v>1876</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>70</v>
@@ -26622,7 +26625,7 @@
         <v>46138</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>1453</v>
+        <v>1876</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>90</v>
@@ -26708,7 +26711,7 @@
         <v>46139</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>1453</v>
+        <v>1876</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>108</v>
@@ -26794,7 +26797,7 @@
         <v>46140</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>1453</v>
+        <v>1876</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>126</v>
@@ -26880,7 +26883,7 @@
         <v>46141</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1453</v>
+        <v>1876</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>144</v>
@@ -26966,7 +26969,7 @@
         <v>46142</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>1453</v>
+        <v>1876</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>29</v>
@@ -27052,7 +27055,7 @@
         <v>46143</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>1453</v>
+        <v>1876</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>51</v>
@@ -27138,7 +27141,7 @@
         <v>46144</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>70</v>
@@ -27224,7 +27227,7 @@
         <v>46145</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>90</v>
@@ -27310,7 +27313,7 @@
         <v>46146</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>108</v>
@@ -27396,7 +27399,7 @@
         <v>46147</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>126</v>
@@ -27482,7 +27485,7 @@
         <v>46148</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>144</v>
@@ -27568,7 +27571,7 @@
         <v>46149</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>29</v>
@@ -27654,7 +27657,7 @@
         <v>46150</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>51</v>
@@ -27740,7 +27743,7 @@
         <v>46151</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>70</v>
@@ -27826,7 +27829,7 @@
         <v>46152</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>90</v>
@@ -27912,7 +27915,7 @@
         <v>46153</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>108</v>
@@ -27998,7 +28001,7 @@
         <v>46154</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>126</v>
@@ -28084,7 +28087,7 @@
         <v>46155</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>144</v>
@@ -28170,7 +28173,7 @@
         <v>46156</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>29</v>
@@ -28256,7 +28259,7 @@
         <v>46157</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>51</v>
@@ -28342,7 +28345,7 @@
         <v>46158</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>70</v>
@@ -28428,7 +28431,7 @@
         <v>46159</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>1876</v>
+        <v>5405</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>90</v>
@@ -28514,7 +28517,7 @@
         <v>46160</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>1876</v>
+        <v>5405</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>108</v>
@@ -28600,7 +28603,7 @@
         <v>46161</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>1876</v>
+        <v>5405</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>126</v>
@@ -28686,7 +28689,7 @@
         <v>46162</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>1876</v>
+        <v>5405</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>144</v>
@@ -28772,7 +28775,7 @@
         <v>46163</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>1876</v>
+        <v>5405</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>29</v>
@@ -28858,7 +28861,7 @@
         <v>46164</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1876</v>
+        <v>5405</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>51</v>
@@ -28944,7 +28947,7 @@
         <v>46165</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>1876</v>
+        <v>5405</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>70</v>
@@ -29030,7 +29033,7 @@
         <v>46166</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>1876</v>
+        <v>5405</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>90</v>
@@ -29116,7 +29119,7 @@
         <v>46167</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>1876</v>
+        <v>5405</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>108</v>
@@ -29202,7 +29205,7 @@
         <v>46168</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>1876</v>
+        <v>5405</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>126</v>
@@ -29288,7 +29291,7 @@
         <v>46169</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>1876</v>
+        <v>5405</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>144</v>
@@ -29374,7 +29377,7 @@
         <v>46170</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>1876</v>
+        <v>5405</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>29</v>
@@ -29460,7 +29463,7 @@
         <v>46171</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>1876</v>
+        <v>5405</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>51</v>
@@ -29546,7 +29549,7 @@
         <v>46172</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>1876</v>
+        <v>5405</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>70</v>
@@ -29632,7 +29635,7 @@
         <v>46173</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>1876</v>
+        <v>5405</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>90</v>
@@ -29718,7 +29721,7 @@
         <v>46174</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>2312</v>
+        <v>5405</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>108</v>
@@ -29804,7 +29807,7 @@
         <v>46175</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>2312</v>
+        <v>5405</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>126</v>
@@ -29890,7 +29893,7 @@
         <v>46176</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>2312</v>
+        <v>5405</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>144</v>
@@ -29976,7 +29979,7 @@
         <v>46177</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>2312</v>
+        <v>5405</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>29</v>
@@ -30062,7 +30065,7 @@
         <v>46178</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>2312</v>
+        <v>5405</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>51</v>
@@ -30148,7 +30151,7 @@
         <v>46179</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>2312</v>
+        <v>5405</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>70</v>
@@ -30234,7 +30237,7 @@
         <v>46180</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>2312</v>
+        <v>5405</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>90</v>
@@ -30320,7 +30323,7 @@
         <v>46181</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>2312</v>
+        <v>5405</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>108</v>
@@ -30406,7 +30409,7 @@
         <v>46182</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>2312</v>
+        <v>5405</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>126</v>
@@ -30492,7 +30495,7 @@
         <v>46183</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>2312</v>
+        <v>5405</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>144</v>
@@ -30578,7 +30581,7 @@
         <v>46184</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>2312</v>
+        <v>5405</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>29</v>
@@ -30664,7 +30667,7 @@
         <v>46185</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>2312</v>
+        <v>5405</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>51</v>
@@ -30750,7 +30753,7 @@
         <v>46186</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>2312</v>
+        <v>5405</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>70</v>
@@ -30836,7 +30839,7 @@
         <v>46187</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>2312</v>
+        <v>5405</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>90</v>
@@ -30922,7 +30925,7 @@
         <v>46188</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>2312</v>
+        <v>5405</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>108</v>
